--- a/data/MO.xlsx
+++ b/data/MO.xlsx
@@ -2808,14 +2808,9 @@
           <t>CAP-C.4</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Activités d'exploitation</t>
-        </is>
-      </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Ajustements</t>
+          <t>= lié à Bénéfices non répartis (reclassement non monétaire)</t>
         </is>
       </c>
     </row>
